--- a/artfynd/A 43333-2023 artfynd.xlsx
+++ b/artfynd/A 43333-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125056379</v>
       </c>
       <c r="B2" t="n">
-        <v>95551</v>
+        <v>95719</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 43333-2023 artfynd.xlsx
+++ b/artfynd/A 43333-2023 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125056379</v>
       </c>
       <c r="B2" t="n">
-        <v>95719</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 43333-2023 artfynd.xlsx
+++ b/artfynd/A 43333-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>125056379</v>
       </c>
       <c r="B2" t="n">
-        <v>95751</v>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,6 +789,200 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125056381</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79486</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Vintersjöhöjden, Gåsborn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>465184</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6640922</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Gåsborn</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125056380</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79413</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6450</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skuggblåslav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hypogymnia vittata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Parrique</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vintersjöhöjden, Gåsborn, Vrm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>465184</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6640928</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Filipstad</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Gåsborn</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-13</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43333-2023 artfynd.xlsx
+++ b/artfynd/A 43333-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -789,6 +794,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125056379</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125056381</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,8 +998,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125056380</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>